--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484378_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484378_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0622</v>
+        <v>6.6052</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2296</v>
+        <v>8.290100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1674</v>
+        <v>-1.6849</v>
       </c>
       <c r="G2" t="n">
         <v>8.3748</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4335</v>
+        <v>-0.0235</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.341</v>
+        <v>-0.2805</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7745</v>
+        <v>0.257</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5507</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>E. SIMS SERRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6913</v>
+        <v>3.2862</v>
       </c>
       <c r="E3" t="n">
-        <v>0.353</v>
+        <v>3.8992</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3383</v>
+        <v>-0.6129</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3738</v>
+        <v>3.7266</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.0639</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3364</v>
+        <v>3.7906</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4794</v>
+        <v>5.9792</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3416</v>
+        <v>0.165</v>
       </c>
       <c r="L3" t="n">
-        <v>1.821</v>
+        <v>5.8142</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8532</v>
+        <v>-2.2526</v>
       </c>
       <c r="N3" t="n">
+        <v>-0.2289</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-2.0237</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.9301</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.4952</v>
+      </c>
+      <c r="T3" t="n">
         <v>-0.3686</v>
       </c>
-      <c r="O3" t="n">
-        <v>-1.4846</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.3674</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1.9534</v>
-      </c>
-      <c r="R3" t="n">
-        <v>3.3208</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.0884</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2726</v>
-      </c>
       <c r="U3" t="n">
-        <v>0.8158</v>
+        <v>-0.1267</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6093</v>
+        <v>0.0549</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0549</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4388</v>
+        <v>2.9199</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4958</v>
+        <v>2.6773</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.057</v>
+        <v>0.2426</v>
       </c>
       <c r="G4" t="n">
         <v>0.1391</v>
@@ -766,13 +766,13 @@
         <v>2.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5403</v>
+        <v>-0.0592</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2805</v>
+        <v>-0.0989</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2598</v>
+        <v>0.0398</v>
       </c>
       <c r="V4" t="n">
         <v>0.8865</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SIMS SERRA</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3673</v>
+        <v>2.2838</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2526</v>
+        <v>0.1906</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8853</v>
+        <v>2.0932</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7266</v>
+        <v>-0.3738</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0639</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7906</v>
+        <v>0.3364</v>
       </c>
       <c r="J5" t="n">
-        <v>5.9792</v>
+        <v>1.4794</v>
       </c>
       <c r="K5" t="n">
-        <v>0.165</v>
+        <v>-0.3416</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8142</v>
+        <v>1.821</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2526</v>
+        <v>-1.8532</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2289</v>
+        <v>-0.3686</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0237</v>
+        <v>-1.4846</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9301</v>
+        <v>3.3208</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4141</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0151</v>
+        <v>0.1102</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.399</v>
+        <v>0.5707</v>
       </c>
       <c r="V5" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X5" t="n">
         <v>0.0549</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.1638</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0273</v>
+        <v>1.8218</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6605</v>
+        <v>2.0944</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6332</v>
+        <v>-0.2726</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9771</v>
+        <v>1.5961</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0473</v>
+        <v>-1.4254</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9297</v>
+        <v>3.0215</v>
       </c>
       <c r="J6" t="n">
-        <v>4.49</v>
+        <v>1.89</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8854</v>
+        <v>0.0819</v>
       </c>
       <c r="L6" t="n">
-        <v>2.6046</v>
+        <v>1.8081</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5129</v>
+        <v>-0.2939</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.838</v>
+        <v>-1.5073</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6749000000000001</v>
+        <v>1.2134</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3441</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4875</v>
+        <v>-0.1417</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5147</v>
+        <v>-0.0728</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0271</v>
+        <v>-0.0689</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8279</v>
+        <v>-0.6093</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4373</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9151</v>
+        <v>1.3843</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2966</v>
+        <v>3.2354</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3816</v>
+        <v>-1.8511</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5961</v>
+        <v>2.9771</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4254</v>
+        <v>1.0473</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0215</v>
+        <v>1.9297</v>
       </c>
       <c r="J7" t="n">
-        <v>1.89</v>
+        <v>4.49</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0819</v>
+        <v>1.8854</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8081</v>
+        <v>2.6046</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2939</v>
+        <v>-1.5129</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5073</v>
+        <v>-0.838</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2134</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>2.3441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0484</v>
+        <v>-0.1555</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1294</v>
+        <v>0.0895</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1778</v>
+        <v>-0.245</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6093</v>
+        <v>-1.8279</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7564</v>
+        <v>0.9236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.287</v>
+        <v>0.5904</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4694</v>
+        <v>0.3332</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2715</v>
@@ -1078,13 +1078,13 @@
         <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3275</v>
+        <v>-0.1603</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.4229</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3988</v>
+        <v>0.2626</v>
       </c>
       <c r="V8" t="n">
         <v>1.5507</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7477</v>
+        <v>-0.485</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2685</v>
+        <v>-0.0058</v>
       </c>
       <c r="F9" t="n">
         <v>-0.4792</v>
@@ -1156,10 +1156,10 @@
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5255</v>
+        <v>-0.2628</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.524</v>
       </c>
       <c r="U9" t="n">
         <v>0.2613</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.181</v>
+        <v>-1.747</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1962</v>
+        <v>-1.0346</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9847</v>
+        <v>-0.7124</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5779</v>
@@ -1234,13 +1234,13 @@
         <v>1.3674</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.084</v>
+        <v>-0.65</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2972</v>
+        <v>-0.0248</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8865</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.808</v>
+        <v>-6.2607</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3127</v>
+        <v>-4.9289</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4953</v>
+        <v>-1.3318</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2569</v>
@@ -1312,13 +1312,13 @@
         <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7659</v>
+        <v>-0.2187</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6657</v>
+        <v>-0.282</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1002</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0503</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.521699999999999</v>
+        <v>10.7321</v>
       </c>
       <c r="E12" t="n">
-        <v>13.7977</v>
+        <v>15.0081</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.276000000000001</v>
+        <v>-4.2759</v>
       </c>
       <c r="G12" t="n">
-        <v>9.697400000000002</v>
+        <v>9.6974</v>
       </c>
       <c r="H12" t="n">
         <v>-2.4444</v>
@@ -1363,7 +1363,7 @@
         <v>12.1417</v>
       </c>
       <c r="J12" t="n">
-        <v>23.8035</v>
+        <v>23.80349999999999</v>
       </c>
       <c r="K12" t="n">
         <v>6.9352</v>
@@ -1390,13 +1390,13 @@
         <v>19.5342</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6963</v>
+        <v>-1.486</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.6855</v>
+        <v>-2.4752</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9892999999999997</v>
+        <v>0.9892000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-1.386</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0157</v>
+        <v>6.2322</v>
       </c>
       <c r="E13" t="n">
         <v>6.3198</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3041</v>
+        <v>-0.0876</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1577</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0682</v>
+        <v>0.2848</v>
       </c>
       <c r="T13" t="n">
         <v>0.0964</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0282</v>
+        <v>0.1883</v>
       </c>
       <c r="V13" t="n">
         <v>4.5424</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5004</v>
+        <v>1.6718</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9506</v>
+        <v>3.7484</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4502</v>
+        <v>-2.0766</v>
       </c>
       <c r="G14" t="n">
         <v>1.2777</v>
@@ -1546,13 +1546,13 @@
         <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3046</v>
+        <v>0.4759</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.341</v>
+        <v>-0.5432</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6456</v>
+        <v>1.0192</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4126</v>
+        <v>1.1702</v>
       </c>
       <c r="E15" t="n">
-        <v>4.63</v>
+        <v>4.2256</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2174</v>
+        <v>-3.0554</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1182</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2453</v>
+        <v>1.0029</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7981</v>
+        <v>0.3936</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4472</v>
+        <v>0.6093</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8865</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1447</v>
+        <v>1.0085</v>
       </c>
       <c r="E16" t="n">
         <v>0.9841</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1606</v>
+        <v>0.0244</v>
       </c>
       <c r="G16" t="n">
         <v>0.6694</v>
@@ -1702,13 +1702,13 @@
         <v>0.1953</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1981</v>
+        <v>0.0619</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3796</v>
+        <v>0.2434</v>
       </c>
       <c r="V16" t="n">
         <v>0.2772</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.732</v>
+        <v>0.6465</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5733</v>
+        <v>2.27</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8414</v>
+        <v>-1.6235</v>
       </c>
       <c r="G17" t="n">
         <v>1.7873</v>
@@ -1780,13 +1780,13 @@
         <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3819</v>
+        <v>0.2965</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5063</v>
+        <v>0.203</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1244</v>
+        <v>0.0935</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8279</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7173</v>
+        <v>-1.1586</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7482</v>
+        <v>-0.2427</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.969</v>
+        <v>-0.9159</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1766</v>
@@ -1858,13 +1858,13 @@
         <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4122</v>
+        <v>0.1465</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6987</v>
+        <v>-0.1931</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2865</v>
+        <v>0.3397</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.132</v>
+        <v>-1.8923</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3112</v>
+        <v>-0.9067</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8208</v>
+        <v>-0.9856</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1443</v>
@@ -1936,13 +1936,13 @@
         <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3896</v>
+        <v>-0.15</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3782</v>
+        <v>-0.9738</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9886</v>
+        <v>0.8238</v>
       </c>
       <c r="V19" t="n">
         <v>2.7693</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.5102</v>
+        <v>-4.0707</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.2379</v>
+        <v>-4.9345</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7276</v>
+        <v>0.8638</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8567</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2861</v>
+        <v>0.1534</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4704</v>
+        <v>-0.1671</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1843</v>
+        <v>0.3205</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0512</v>
+        <v>-6.1834</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9344</v>
+        <v>-4.3389</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1169</v>
+        <v>-1.8445</v>
       </c>
       <c r="G21" t="n">
         <v>-5.784</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8778</v>
+        <v>0.7457</v>
       </c>
       <c r="T21" t="n">
-        <v>0.677</v>
+        <v>0.2726</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2008</v>
+        <v>0.4731</v>
       </c>
       <c r="V21" t="n">
         <v>0.2224</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9162</v>
+        <v>-6.2718</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9501</v>
+        <v>-2.849</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.9661</v>
+        <v>-3.4228</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1942</v>
@@ -2170,13 +2170,13 @@
         <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2916</v>
+        <v>0.3529</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0029</v>
+        <v>0.104</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2945</v>
+        <v>0.2489</v>
       </c>
       <c r="V22" t="n">
         <v>-1.9376</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.521500000000001</v>
+        <v>-8.847600000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>4.275999999999999</v>
+        <v>4.2761</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.7977</v>
+        <v>-13.1237</v>
       </c>
       <c r="G23" t="n">
         <v>-9.6973</v>
@@ -2248,13 +2248,13 @@
         <v>15.6273</v>
       </c>
       <c r="S23" t="n">
-        <v>2.696400000000001</v>
+        <v>3.3705</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9891999999999997</v>
+        <v>-0.9892000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>3.6855</v>
+        <v>4.359699999999999</v>
       </c>
       <c r="V23" t="n">
         <v>1.386199999999999</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484378_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484378_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. SABATÉS SALA</t>
+          <t>G. SABATES SALA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-0.8865</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.0503</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-10.6933</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,11 +1624,16 @@
       <c r="X14" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1702</v>
+        <v>1.5349</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2256</v>
+        <v>1.5349</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.0554</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1182</v>
+        <v>1.5349</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2428</v>
+        <v>1.5349</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.361</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.418</v>
+        <v>1.5349</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2157</v>
+        <v>1.5349</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2023</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.5362</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9729</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.5634</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0029</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3936</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. FLOREN LARIO</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0085</v>
+        <v>1.1702</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9841</v>
+        <v>4.2256</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0244</v>
+        <v>-3.0554</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6694</v>
+        <v>-0.1182</v>
       </c>
       <c r="H16" t="n">
-        <v>0.319</v>
+        <v>2.2428</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3504</v>
+        <v>-2.361</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0838</v>
+        <v>3.418</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0028</v>
+        <v>3.2157</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>0.2023</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4144</v>
+        <v>-3.5362</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6838</v>
+        <v>-0.9729</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>-2.5634</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0619</v>
+        <v>1.0029</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1816</v>
+        <v>0.3936</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2434</v>
+        <v>0.6093</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. VIDAL RAMOS</t>
+          <t>D. FLOREN LARIO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6465</v>
+        <v>1.0085</v>
       </c>
       <c r="E17" t="n">
-        <v>2.27</v>
+        <v>0.9841</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6235</v>
+        <v>0.0244</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7873</v>
+        <v>0.6694</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3832</v>
+        <v>0.319</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4041</v>
+        <v>0.3504</v>
       </c>
       <c r="J17" t="n">
-        <v>2.067</v>
+        <v>1.0838</v>
       </c>
       <c r="K17" t="n">
-        <v>2.067</v>
+        <v>1.0028</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2797</v>
+        <v>-0.4144</v>
       </c>
       <c r="N17" t="n">
         <v>-0.6838</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4041</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2965</v>
+        <v>0.0619</v>
       </c>
       <c r="T17" t="n">
-        <v>0.203</v>
+        <v>-0.1816</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0935</v>
+        <v>0.2434</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>F. VIDAL RAMOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1586</v>
+        <v>0.6465</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2427</v>
+        <v>2.27</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9159</v>
+        <v>-1.6235</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1766</v>
+        <v>1.7873</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3346</v>
+        <v>1.3832</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5112</v>
+        <v>0.4041</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9272</v>
+        <v>2.067</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1445</v>
+        <v>2.067</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7827</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1038</v>
+        <v>-0.2797</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1901</v>
+        <v>-0.6838</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.2939</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1465</v>
+        <v>0.2965</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1931</v>
+        <v>0.203</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3397</v>
+        <v>0.0935</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>-1.8279</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8923</v>
+        <v>-1.1586</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9067</v>
+        <v>-0.2427</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9856</v>
+        <v>-0.9159</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1443</v>
+        <v>-1.1766</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0.3346</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5894</v>
+        <v>-1.5112</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9273</v>
+        <v>0.9272</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.261</v>
+        <v>0.1445</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1883</v>
+        <v>0.7827</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.0716</v>
+        <v>-2.1038</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2939</v>
+        <v>0.1901</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.7777</v>
+        <v>-2.2939</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3674</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9069</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.15</v>
+        <v>0.1465</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9738</v>
+        <v>-0.1931</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8238</v>
+        <v>0.3397</v>
       </c>
       <c r="V19" t="n">
-        <v>2.7693</v>
+        <v>-1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>3.0466</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. RAMOS SAINZ</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0707</v>
+        <v>-1.8923</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.9345</v>
+        <v>-0.9067</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8638</v>
+        <v>-0.9856</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.8567</v>
+        <v>-3.1443</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2047</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.0614</v>
+        <v>-2.5894</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8373</v>
+        <v>0.9273</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1445</v>
+        <v>-0.261</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9818</v>
+        <v>1.1883</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0194</v>
+        <v>-4.0716</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0601</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0795</v>
+        <v>-3.7777</v>
       </c>
       <c r="P20" t="n">
         <v>-1.3674</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-3.9069</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1534</v>
+        <v>-0.15</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1671</v>
+        <v>-0.9738</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3205</v>
+        <v>0.8238</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.7693</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>P. RAMOS SAINZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.1834</v>
+        <v>-4.0707</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3389</v>
+        <v>-4.9345</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8445</v>
+        <v>0.8638</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.784</v>
+        <v>-2.8567</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7361</v>
+        <v>0.2047</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.048</v>
+        <v>-3.0614</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7083</v>
+        <v>-1.8373</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9543</v>
+        <v>0.1445</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.754</v>
+        <v>-1.9818</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.0757</v>
+        <v>-1.0194</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7818</v>
+        <v>0.0601</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.2939</v>
+        <v>-1.0795</v>
       </c>
       <c r="P21" t="n">
         <v>-1.3674</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7457</v>
+        <v>0.1534</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2726</v>
+        <v>-0.1671</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4731</v>
+        <v>0.3205</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2718</v>
+        <v>-6.1834</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.849</v>
+        <v>-4.3389</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4228</v>
+        <v>-1.8445</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1942</v>
+        <v>-5.784</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9762</v>
+        <v>-2.7361</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7821</v>
+        <v>-3.048</v>
       </c>
       <c r="J22" t="n">
-        <v>2.603</v>
+        <v>-1.7083</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7406</v>
+        <v>-0.9543</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8624</v>
+        <v>-0.754</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7971</v>
+        <v>-4.0757</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7168</v>
+        <v>-1.7818</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0803</v>
+        <v>-2.2939</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.4929</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.0556</v>
+        <v>-3.1255</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3529</v>
+        <v>0.7457</v>
       </c>
       <c r="T22" t="n">
-        <v>0.104</v>
+        <v>0.2726</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2489</v>
+        <v>0.4731</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9376</v>
+        <v>0.2224</v>
       </c>
       <c r="W22" t="n">
-        <v>0.4996</v>
+        <v>0.2224</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-7.8067</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-4.3839</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.4228</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.7291</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.5112</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7821</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.0681</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.7944</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.8624</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.7971</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.7168</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.0803</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-4.4929</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-6.0556</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.9376</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484378_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-8.847600000000002</v>
       </c>
-      <c r="E23" t="n">
-        <v>4.2761</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E24" t="n">
+        <v>4.276100000000004</v>
+      </c>
+      <c r="F24" t="n">
         <v>-13.1237</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-9.6973</v>
       </c>
-      <c r="H23" t="n">
-        <v>2.444299999999999</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H24" t="n">
+        <v>2.444199999999999</v>
+      </c>
+      <c r="I24" t="n">
         <v>-12.1416</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>14.1061</v>
       </c>
-      <c r="K23" t="n">
-        <v>9.3794</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K24" t="n">
+        <v>9.379300000000002</v>
+      </c>
+      <c r="L24" t="n">
         <v>4.726599999999999</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-23.8033</v>
       </c>
-      <c r="N23" t="n">
-        <v>-6.9352</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="N24" t="n">
+        <v>-6.935200000000001</v>
+      </c>
+      <c r="O24" t="n">
         <v>-16.8682</v>
       </c>
-      <c r="P23" t="n">
-        <v>-3.906899999999999</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="P24" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-19.5342</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>15.6273</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>3.3705</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>-0.9892000000000002</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>4.359699999999999</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.386199999999999</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V24" t="n">
+        <v>1.3862</v>
+      </c>
+      <c r="W24" t="n">
         <v>10.6934</v>
       </c>
-      <c r="X23" t="n">
-        <v>-9.307300000000001</v>
-      </c>
+      <c r="X24" t="n">
+        <v>-9.3073</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
